--- a/Project_Tracker_MultiSelect.xlsx
+++ b/Project_Tracker_MultiSelect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Trackers script\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e63e5e337b037366/Desktop/Semester4/Introduction to Data Scienece/PROJECT-IDS-LOAN-APPROVAL-n/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAEFAC3-544E-4B0D-B04A-CC2EE40F6CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{5EAEFAC3-544E-4B0D-B04A-CC2EE40F6CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A6881AE-8C25-4D8E-B5D2-AE2D59611E29}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>Sr No</t>
   </si>
@@ -61,6 +61,27 @@
   </si>
   <si>
     <t>Actual Submission</t>
+  </si>
+  <si>
+    <t>Central Tendency(Mean, Mode, Median)</t>
+  </si>
+  <si>
+    <t>Farooq</t>
+  </si>
+  <si>
+    <t>Sayam</t>
+  </si>
+  <si>
+    <t>Outlier and Box Plot</t>
+  </si>
+  <si>
+    <t>Azfar</t>
+  </si>
+  <si>
+    <t>Data Symmetry / Word Document Review</t>
+  </si>
+  <si>
+    <t>Laiba</t>
   </si>
 </sst>
 </file>
@@ -597,21 +618,76 @@
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="str">
-        <f t="shared" ref="A3:A34" si="0">IF(B3&lt;&gt;"", ROW()-2, "")</f>
-        <v/>
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46155</v>
+      </c>
+      <c r="G3" s="2">
+        <f>F3+3</f>
+        <v>46158</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A4" s="1">
+        <f t="shared" ref="A3:A34" si="0">IF(B4&lt;&gt;"", ROW()-2, "")</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46155</v>
+      </c>
+      <c r="G4" s="2">
+        <f>F3+3</f>
+        <v>46158</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46155</v>
+      </c>
+      <c r="G5" s="2">
+        <f>F3+3</f>
+        <v>46158</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -1174,7 +1250,7 @@
     </row>
     <row r="99" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="str">
-        <f t="shared" ref="A99:A130" si="3">IF(B99&lt;&gt;"", ROW()-2, "")</f>
+        <f t="shared" ref="A99:A101" si="3">IF(B99&lt;&gt;"", ROW()-2, "")</f>
         <v/>
       </c>
     </row>

--- a/Project_Tracker_MultiSelect.xlsx
+++ b/Project_Tracker_MultiSelect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e63e5e337b037366/Desktop/Semester4/Introduction to Data Scienece/PROJECT-IDS-LOAN-APPROVAL-n/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FAroOq UNIVERSITY\4th Semester\Intro to Data Science\PROJECT-IDS-LOAN-APPROVAL-n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{5EAEFAC3-544E-4B0D-B04A-CC2EE40F6CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A6881AE-8C25-4D8E-B5D2-AE2D59611E29}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD70FE1-A6FE-422B-9818-9863ABF07A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -637,13 +637,15 @@
         <v>46155</v>
       </c>
       <c r="G3" s="2">
-        <f>F3+3</f>
-        <v>46158</v>
+        <v>46159</v>
+      </c>
+      <c r="H3" s="2">
+        <v>46159</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <f t="shared" ref="A3:A34" si="0">IF(B4&lt;&gt;"", ROW()-2, "")</f>
+        <f t="shared" ref="A4:A34" si="0">IF(B4&lt;&gt;"", ROW()-2, "")</f>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -662,8 +664,10 @@
         <v>46155</v>
       </c>
       <c r="G4" s="2">
-        <f>F3+3</f>
-        <v>46158</v>
+        <v>46159</v>
+      </c>
+      <c r="H4" s="2">
+        <v>46159</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -686,8 +690,10 @@
         <v>46155</v>
       </c>
       <c r="G5" s="2">
-        <f>F3+3</f>
-        <v>46158</v>
+        <v>46159</v>
+      </c>
+      <c r="H5" s="2">
+        <v>46159</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">

--- a/Project_Tracker_MultiSelect.xlsx
+++ b/Project_Tracker_MultiSelect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FAroOq UNIVERSITY\4th Semester\Intro to Data Science\PROJECT-IDS-LOAN-APPROVAL-n\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e63e5e337b037366/Desktop/Semester4/Introduction to Data Scienece/PROJECT-IDS-LOAN-APPROVAL-n/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD70FE1-A6FE-422B-9818-9863ABF07A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{CCD70FE1-A6FE-422B-9818-9863ABF07A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{999D692E-A628-4982-97DD-2835F7ABCF7F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
   <si>
     <t>Sr No</t>
   </si>
@@ -82,6 +82,18 @@
   </si>
   <si>
     <t>Laiba</t>
+  </si>
+  <si>
+    <t>Formatting Techniques Overview</t>
+  </si>
+  <si>
+    <t>Normalization Technique Overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Handling Missing Data Overview</t>
+  </si>
+  <si>
+    <t>Removing Noise Data Overview</t>
   </si>
 </sst>
 </file>
@@ -697,27 +709,99 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G6" s="2">
+        <v>46187</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G7" s="2">
+        <v>46187</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G8" s="2">
+        <v>46187</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46187</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">

--- a/Project_Tracker_MultiSelect.xlsx
+++ b/Project_Tracker_MultiSelect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e63e5e337b037366/Desktop/Semester4/Introduction to Data Scienece/PROJECT-IDS-LOAN-APPROVAL-n/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FAroOq UNIVERSITY\4th Semester\Intro to Data Science\PROJECT-IDS-LOAN-APPROVAL-n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{CCD70FE1-A6FE-422B-9818-9863ABF07A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{999D692E-A628-4982-97DD-2835F7ABCF7F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77B4E60-27CC-4E92-9AA6-BE0CAD7EC8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -731,6 +731,9 @@
       <c r="G6" s="2">
         <v>46187</v>
       </c>
+      <c r="H6" s="2">
+        <v>46187</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
@@ -755,6 +758,9 @@
       <c r="G7" s="2">
         <v>46187</v>
       </c>
+      <c r="H7" s="2">
+        <v>46187</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
@@ -779,6 +785,9 @@
       <c r="G8" s="2">
         <v>46187</v>
       </c>
+      <c r="H8" s="2">
+        <v>46187</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -801,6 +810,9 @@
         <v>46186</v>
       </c>
       <c r="G9" s="2">
+        <v>46187</v>
+      </c>
+      <c r="H9" s="2">
         <v>46187</v>
       </c>
     </row>
